--- a/excel/output_stats_sfvv/gemver/PerSubgraphStats.xlsx
+++ b/excel/output_stats_sfvv/gemver/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,10 +1199,10 @@
         <v>0.6</v>
       </c>
       <c r="N16" t="n">
-        <v>351.242</v>
+        <v>353.452</v>
       </c>
       <c r="O16" t="n">
-        <v>353.45</v>
+        <v>355.66</v>
       </c>
     </row>
     <row r="17">
@@ -1246,10 +1246,10 @@
         <v>0.6</v>
       </c>
       <c r="N17" t="n">
-        <v>351.242</v>
+        <v>353.452</v>
       </c>
       <c r="O17" t="n">
-        <v>353.46</v>
+        <v>355.68</v>
       </c>
     </row>
     <row r="18">
@@ -1257,34 +1257,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>1.7545e-09</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.33333e-09</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.277026</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.11118e-17</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>947368000</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>3000000000</v>
@@ -1293,10 +1293,10 @@
         <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>350.151</v>
+        <v>352.358</v>
       </c>
       <c r="O18" t="n">
-        <v>350.18</v>
+        <v>354.61</v>
       </c>
     </row>
     <row r="19">
@@ -1304,35 +1304,35 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.7545e-09</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.33333e-09</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.277026</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.11118e-17</v>
+      </c>
+      <c r="G19" t="n">
+        <v>947368000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
         <v>19</v>
       </c>
-      <c r="C19" t="n">
-        <v>7.62835e-07</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.8112e-06</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.271356</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.14448e-12</v>
-      </c>
-      <c r="G19" t="n">
-        <v>882353000</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2480.47</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2232.42</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8433.59</v>
-      </c>
       <c r="L19" t="n">
         <v>3000000000</v>
       </c>
@@ -1340,10 +1340,10 @@
         <v>0.6</v>
       </c>
       <c r="N19" t="n">
-        <v>350.151</v>
+        <v>352.354</v>
       </c>
       <c r="O19" t="n">
-        <v>350.23</v>
+        <v>354.6</v>
       </c>
     </row>
     <row r="20">
@@ -1351,34 +1351,34 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>9.13256e-10</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.66667e-09</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.342471</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2.43535e-18</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3000000000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>3000000000</v>
@@ -1387,10 +1387,10 @@
         <v>0.6</v>
       </c>
       <c r="N20" t="n">
-        <v>351.244</v>
+        <v>352.354</v>
       </c>
       <c r="O20" t="n">
-        <v>353.48</v>
+        <v>354.59</v>
       </c>
     </row>
     <row r="21">
@@ -1398,34 +1398,34 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00492643</v>
+        <v>7.62835e-07</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0186607</v>
+        <v>2.8112e-06</v>
       </c>
       <c r="E21" t="n">
-        <v>0.264001</v>
+        <v>0.271356</v>
       </c>
       <c r="F21" t="n">
-        <v>9.19305e-05</v>
+        <v>2.14448e-12</v>
       </c>
       <c r="G21" t="n">
-        <v>750134000</v>
+        <v>882353000</v>
       </c>
       <c r="H21" t="n">
-        <v>13998000</v>
+        <v>2480.47</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>12997500</v>
+        <v>2232.42</v>
       </c>
       <c r="K21" t="n">
-        <v>55982000</v>
+        <v>8433.59</v>
       </c>
       <c r="L21" t="n">
         <v>3000000000</v>
@@ -1434,10 +1434,10 @@
         <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>351.244</v>
+        <v>352.358</v>
       </c>
       <c r="O21" t="n">
-        <v>353.49</v>
+        <v>354.61</v>
       </c>
     </row>
     <row r="22">
@@ -1445,34 +1445,34 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00314142</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0120604</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.260474</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>3.78867e-05</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>781215000</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9421750</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>8922400</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>36181200</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>3000000000</v>
@@ -1481,10 +1481,10 @@
         <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>351.255</v>
+        <v>352.354</v>
       </c>
       <c r="O22" t="n">
-        <v>353.5</v>
+        <v>354.59</v>
       </c>
     </row>
     <row r="23">
@@ -1492,34 +1492,34 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>8.27904e-09</v>
+        <v>9.13256e-10</v>
       </c>
       <c r="D23" t="n">
-        <v>2.9e-08</v>
+        <v>2.66667e-09</v>
       </c>
       <c r="E23" t="n">
-        <v>0.285484</v>
+        <v>0.342471</v>
       </c>
       <c r="F23" t="n">
-        <v>2.40092e-16</v>
+        <v>2.43535e-18</v>
       </c>
       <c r="G23" t="n">
-        <v>1655170000</v>
+        <v>3000000000</v>
       </c>
       <c r="H23" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
         <v>3000000000</v>
@@ -1528,10 +1528,10 @@
         <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>350.151</v>
+        <v>352.354</v>
       </c>
       <c r="O23" t="n">
-        <v>350.22</v>
+        <v>354.59</v>
       </c>
     </row>
     <row r="24">
@@ -1539,34 +1539,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>1.79687e-08</v>
+        <v>0.00492643</v>
       </c>
       <c r="D24" t="n">
-        <v>6.7e-08</v>
+        <v>0.0186607</v>
       </c>
       <c r="E24" t="n">
-        <v>0.26819</v>
+        <v>0.264001</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2039e-15</v>
+        <v>9.19305e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>925373000</v>
+        <v>750134000</v>
       </c>
       <c r="H24" t="n">
-        <v>62</v>
+        <v>13998000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>36</v>
+        <v>12997500</v>
       </c>
       <c r="K24" t="n">
-        <v>201</v>
+        <v>55982000</v>
       </c>
       <c r="L24" t="n">
         <v>3000000000</v>
@@ -1575,10 +1575,10 @@
         <v>0.6</v>
       </c>
       <c r="N24" t="n">
-        <v>350.15</v>
+        <v>352.354</v>
       </c>
       <c r="O24" t="n">
-        <v>350.18</v>
+        <v>354.61</v>
       </c>
     </row>
     <row r="25">
@@ -1586,25 +1586,25 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>4.76522e-10</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>2e-09</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.238261</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>9.530439999999999e-19</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>500000000</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>3000000000</v>
@@ -1622,10 +1622,10 @@
         <v>0.6</v>
       </c>
       <c r="N25" t="n">
-        <v>350.15</v>
+        <v>351.255</v>
       </c>
       <c r="O25" t="n">
-        <v>350.17</v>
+        <v>353.49</v>
       </c>
     </row>
     <row r="26">
@@ -1633,34 +1633,34 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>4.76522e-10</v>
+        <v>0.00314142</v>
       </c>
       <c r="D26" t="n">
-        <v>2e-09</v>
+        <v>0.0120604</v>
       </c>
       <c r="E26" t="n">
-        <v>0.238261</v>
+        <v>0.260474</v>
       </c>
       <c r="F26" t="n">
-        <v>9.530439999999999e-19</v>
+        <v>3.78867e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>500000000</v>
+        <v>781215000</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>9421750</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>8922400</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>36181200</v>
       </c>
       <c r="L26" t="n">
         <v>3000000000</v>
@@ -1669,10 +1669,10 @@
         <v>0.6</v>
       </c>
       <c r="N26" t="n">
-        <v>350.15</v>
+        <v>351.255</v>
       </c>
       <c r="O26" t="n">
-        <v>350.17</v>
+        <v>353.5</v>
       </c>
     </row>
     <row r="27">
@@ -1680,34 +1680,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>6.24265e-10</v>
+        <v>8.27904e-09</v>
       </c>
       <c r="D27" t="n">
-        <v>2.33333e-09</v>
+        <v>2.9e-08</v>
       </c>
       <c r="E27" t="n">
-        <v>0.267542</v>
+        <v>0.285484</v>
       </c>
       <c r="F27" t="n">
-        <v>1.45662e-18</v>
+        <v>2.40092e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>857143000</v>
+        <v>1655170000</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="L27" t="n">
         <v>3000000000</v>
@@ -1719,7 +1719,7 @@
         <v>350.151</v>
       </c>
       <c r="O27" t="n">
-        <v>350.17</v>
+        <v>350.22</v>
       </c>
     </row>
     <row r="28">
@@ -1727,34 +1727,34 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>6.24265e-10</v>
+        <v>1.79687e-08</v>
       </c>
       <c r="D28" t="n">
-        <v>2.33333e-09</v>
+        <v>6.7e-08</v>
       </c>
       <c r="E28" t="n">
-        <v>0.267542</v>
+        <v>0.26819</v>
       </c>
       <c r="F28" t="n">
-        <v>1.45662e-18</v>
+        <v>1.2039e-15</v>
       </c>
       <c r="G28" t="n">
-        <v>857143000</v>
+        <v>925373000</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="L28" t="n">
         <v>3000000000</v>
@@ -1763,10 +1763,10 @@
         <v>0.6</v>
       </c>
       <c r="N28" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O28" t="n">
-        <v>350.17</v>
+        <v>350.18</v>
       </c>
     </row>
     <row r="29">
@@ -1774,34 +1774,34 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>1.48585e-09</v>
+        <v>4.76522e-10</v>
       </c>
       <c r="D29" t="n">
-        <v>5.66667e-09</v>
+        <v>2e-09</v>
       </c>
       <c r="E29" t="n">
-        <v>0.262208</v>
+        <v>0.238261</v>
       </c>
       <c r="F29" t="n">
-        <v>8.419790000000001e-18</v>
+        <v>9.530439999999999e-19</v>
       </c>
       <c r="G29" t="n">
-        <v>705882000</v>
+        <v>500000000</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
         <v>3000000000</v>
@@ -1821,22 +1821,22 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>1.21265e-10</v>
+        <v>4.76522e-10</v>
       </c>
       <c r="D30" t="n">
-        <v>3.33333e-10</v>
+        <v>2e-09</v>
       </c>
       <c r="E30" t="n">
-        <v>0.363794</v>
+        <v>0.238261</v>
       </c>
       <c r="F30" t="n">
-        <v>4.04216e-20</v>
+        <v>9.530439999999999e-19</v>
       </c>
       <c r="G30" t="n">
-        <v>3000000000</v>
+        <v>500000000</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1848,18 +1848,206 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="O30" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6.24265e-10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.33333e-09</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.267542</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.45662e-18</v>
+      </c>
+      <c r="G31" t="n">
+        <v>857143000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>3000000000</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="K31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N31" t="n">
         <v>350.151</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O31" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6.24265e-10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.33333e-09</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.267542</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.45662e-18</v>
+      </c>
+      <c r="G32" t="n">
+        <v>857143000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O32" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.48585e-09</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5.66667e-09</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.262208</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8.419790000000001e-18</v>
+      </c>
+      <c r="G33" t="n">
+        <v>705882000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>17</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N33" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="O33" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.21265e-10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.33333e-10</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.363794</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.04216e-20</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O34" t="n">
         <v>350.22</v>
       </c>
     </row>
